--- a/hist_data.xlsx
+++ b/hist_data.xlsx
@@ -1,57 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A0117-9C0F-D14E-AA2B-5ED8A8107EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>階級（点数）</t>
+    <t>出席番号</t>
   </si>
   <si>
-    <t>度数（人）</t>
-  </si>
-  <si>
-    <t>0 ～ 9</t>
-  </si>
-  <si>
-    <t>10 ～ 19</t>
-  </si>
-  <si>
-    <t>20 ～ 29</t>
-  </si>
-  <si>
-    <t>30 ～ 39</t>
-  </si>
-  <si>
-    <t>40 ～ 49</t>
-  </si>
-  <si>
-    <t>50 ～ 59</t>
-  </si>
-  <si>
-    <t>60 ～ 69</t>
+    <t>数学のテスト結果</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -59,8 +44,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -106,17 +98,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -154,7 +154,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -188,6 +188,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -222,9 +223,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -397,9 +399,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -410,62 +412,247 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+      <c r="B6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
+      <c r="B7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
         <v>6</v>
       </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/hist_data.xlsx
+++ b/hist_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910A0117-9C0F-D14E-AA2B-5ED8A8107EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB51193-C0EE-0040-A69C-5B22EB7DEEF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="500" windowWidth="25600" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,18 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>出席番号</t>
+    <t>計測日</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ケイソクビ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>数学のテスト結果</t>
+    <t>気温</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">キオン </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -400,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -416,7 +424,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -424,7 +432,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -432,7 +440,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -440,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -448,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -456,7 +464,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -464,7 +472,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -472,7 +480,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -480,7 +488,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -488,7 +496,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -496,7 +504,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -504,7 +512,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -512,7 +520,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -520,7 +528,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -528,7 +536,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -536,7 +544,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>54</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -544,7 +552,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -552,7 +560,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -560,7 +568,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -568,7 +576,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -576,7 +584,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -584,7 +592,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>50</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -592,7 +600,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -600,7 +608,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>49</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -608,7 +616,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -616,7 +624,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -624,7 +632,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -632,7 +640,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -640,7 +648,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -648,7 +656,287 @@
         <v>30</v>
       </c>
       <c r="B31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
         <v>65</v>
+      </c>
+      <c r="B66">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
